--- a/RESTful-booker-service-api.xlsx
+++ b/RESTful-booker-service-api.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\proget\restful-booker\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="236">
   <si>
     <t>HIGH</t>
   </si>
@@ -102,42 +102,12 @@
     <t>1. User fetches list of bookings with checkout date query parameter</t>
   </si>
   <si>
-    <t>TC_FT_AUTH_POS_001</t>
-  </si>
-  <si>
-    <t>TC_FT_AUTH_NEG_003</t>
-  </si>
-  <si>
-    <t>TC_FT_AUTH_NEG_002</t>
-  </si>
-  <si>
-    <t>TC_FT_BOOKING_POS_001</t>
-  </si>
-  <si>
-    <t>TC_FT_AUTH_NEG_001</t>
-  </si>
-  <si>
-    <t>TC_FT_BOOKING_POS_002</t>
-  </si>
-  <si>
-    <t>TC_FT_BOOKING_POS_003</t>
-  </si>
-  <si>
-    <t>TC_FT_BOOKING_POS_004</t>
-  </si>
-  <si>
-    <t>TC_FT_BOOKING_POS_005</t>
-  </si>
-  <si>
     <t>1.4 Getting list of bookings after checkin date</t>
   </si>
   <si>
     <t>1.5 Getting list of bookings after checkout date</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_001</t>
-  </si>
-  <si>
     <t>1. User fetches list of bookings with invalid checkin date</t>
   </si>
   <si>
@@ -150,24 +120,15 @@
     <t>FAIL</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_002</t>
-  </si>
-  <si>
     <t>1. User fetches list of bookings with invalid checkin date format</t>
   </si>
   <si>
     <t>Response with the IDs of all the bookings after the specified checkin date with invalid format and OK [200] status</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_003</t>
-  </si>
-  <si>
     <t>1. User fetches list of bookings with invalid checkout date</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_004</t>
-  </si>
-  <si>
     <t>1. User fetches list of bookings with invalid checkout date format</t>
   </si>
   <si>
@@ -192,12 +153,6 @@
     <t>1.4 Getting bookings by invalid checkout date format</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_005</t>
-  </si>
-  <si>
-    <t>TC_FT_BOOKING_POS_006</t>
-  </si>
-  <si>
     <t>1. User fetches booking by ID</t>
   </si>
   <si>
@@ -222,18 +177,9 @@
     <t>Response with a specific booking based upon the booking ID provided with OK [200] status</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_POS_007</t>
-  </si>
-  <si>
     <t>1. User fetches booking by ID with HTTP header "Accept: application/xml"</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_POS_008</t>
-  </si>
-  <si>
-    <t>TC_FT_BOOKING_NEG_008</t>
-  </si>
-  <si>
     <t>2.1 Getting booking in JSON format</t>
   </si>
   <si>
@@ -249,9 +195,6 @@
     <t>Response with Not Found [404] status</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_006</t>
-  </si>
-  <si>
     <t>2.1.1 Getting booking by non-existing ID</t>
   </si>
   <si>
@@ -264,21 +207,12 @@
     <t>Response with the IDs of all the bookings filtered after booking "checkout" date query parameter with OK [200] status</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_007</t>
-  </si>
-  <si>
     <t>2.2.1 Getting booking by non-existing ID</t>
   </si>
   <si>
     <t>2.2.2 Getting booking by non-numeric ID</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_009</t>
-  </si>
-  <si>
-    <t>TC_FT_BOOKING_POS_009</t>
-  </si>
-  <si>
     <t>3.1 Create new booking</t>
   </si>
   <si>
@@ -288,9 +222,6 @@
     <t>Response with new booking with OK [200] status</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_POS_010</t>
-  </si>
-  <si>
     <t>3.2 Create new booking with nullable property additionalneeds</t>
   </si>
   <si>
@@ -300,9 +231,6 @@
     <t>Response with new booking with nullable property "additionalneeds" with OK [200] status</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_POS_011</t>
-  </si>
-  <si>
     <t>3.3 Create new booking with missing property additionalneeds</t>
   </si>
   <si>
@@ -321,9 +249,6 @@
     <t>Response with new booking with missing property "additionalneeds" and OK [200] status</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_POS_012</t>
-  </si>
-  <si>
     <t>3.4 Create new booking with empty property additionalneeds</t>
   </si>
   <si>
@@ -336,33 +261,21 @@
     <t>Response with new booking with empty property "additionalneeds" and OK [200] status</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_013</t>
-  </si>
-  <si>
     <t>3.1 Create new booking with nullable property firstname</t>
   </si>
   <si>
     <t>1. User creates new booking with nullable property "firstname"</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_010</t>
-  </si>
-  <si>
     <t>Response with new booking with empty property "firstname" and OK [200] status</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_011</t>
-  </si>
-  <si>
     <t>3.2 Create new booking with empty property firstname</t>
   </si>
   <si>
     <t>3.3 Create new booking with nullable lastname</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_012</t>
-  </si>
-  <si>
     <t>3.4 Create new booking with empty property lastname</t>
   </si>
   <si>
@@ -381,9 +294,6 @@
     <t>3.5 Create new booking with nullable property totalprice</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_014</t>
-  </si>
-  <si>
     <t>3.6 Create new booking with negative property totalprice</t>
   </si>
   <si>
@@ -396,21 +306,12 @@
     <t>Response with new booking with negative property "totalprice" and OK [200] status</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_015</t>
-  </si>
-  <si>
     <t>3.7 Create new booking with nullable property depositpaid</t>
   </si>
   <si>
     <t>1. User creates new booking with nullable property "depositpaid"</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_016</t>
-  </si>
-  <si>
-    <t>TC_FT_BOOKING_NEG_017</t>
-  </si>
-  <si>
     <t>3.8 Create new booking with nullable property bookindates</t>
   </si>
   <si>
@@ -423,21 +324,6 @@
     <t>Response with new booking with booking checkin date after booking checkout date and OK [200] status</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_018</t>
-  </si>
-  <si>
-    <t>TC_FT_BOOKING_NEG_019</t>
-  </si>
-  <si>
-    <t>TC_FT_BOOKING_NEG_020</t>
-  </si>
-  <si>
-    <t>TC_FT_BOOKING_NEG_021</t>
-  </si>
-  <si>
-    <t>TC_FT_BOOKING_NEG_022</t>
-  </si>
-  <si>
     <t>3.10 Create new booking with booking checkin date same as booking checkout date</t>
   </si>
   <si>
@@ -474,9 +360,6 @@
     <t>3.14 Create new booking with empty property booking checkin date</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_023</t>
-  </si>
-  <si>
     <t>3.15 Create new booking with emtpy property booking checkout date</t>
   </si>
   <si>
@@ -486,9 +369,6 @@
     <t>1. User creates new booking with emtpy property booking "checkout" date</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_024</t>
-  </si>
-  <si>
     <t>4.1 Update booking</t>
   </si>
   <si>
@@ -507,18 +387,12 @@
     <t>Response with method not allowed [405] status</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_025</t>
-  </si>
-  <si>
     <t>4.2 Update booking by non-numeric ID</t>
   </si>
   <si>
     <t>1. User updates booking by non-numeric ID</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_026</t>
-  </si>
-  <si>
     <t>4.3 Update booking by ID with missing auth header</t>
   </si>
   <si>
@@ -531,12 +405,6 @@
     <t>Response with Forbidden [403] status</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_027</t>
-  </si>
-  <si>
-    <t>TC_FT_BOOKING_NEG_028</t>
-  </si>
-  <si>
     <t>1. User updates booking by ID with invalid auth token</t>
   </si>
   <si>
@@ -564,24 +432,15 @@
     <t>1. User updates partially booking by ID</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_029</t>
-  </si>
-  <si>
     <t>5.2 Update partially booking by non-numeric ID</t>
   </si>
   <si>
     <t>1. User updates partially booking by non-numeric ID</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_030</t>
-  </si>
-  <si>
     <t>1. User updates partially booking by ID with missing auth header</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_031</t>
-  </si>
-  <si>
     <t>5.3 Update partially booking by ID with missing auth header</t>
   </si>
   <si>
@@ -591,9 +450,6 @@
     <t>1. User updates partially booking by ID with invalid auth token</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_032</t>
-  </si>
-  <si>
     <t>6.1 Delete booking</t>
   </si>
   <si>
@@ -618,12 +474,6 @@
     <t>1. User deletes booking by non-existing ID</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_033</t>
-  </si>
-  <si>
-    <t>TC_FT_BOOKING_NEG_034</t>
-  </si>
-  <si>
     <t>6.2 Delete booking by non-numeric ID</t>
   </si>
   <si>
@@ -636,9 +486,6 @@
     <t>1. User deletes booking by ID with missing auth header</t>
   </si>
   <si>
-    <t>TC_FT_BOOKING_NEG_035</t>
-  </si>
-  <si>
     <t>6.4 Delete booking by ID with invalid auth token</t>
   </si>
   <si>
@@ -669,9 +516,6 @@
     <t>Booking</t>
   </si>
   <si>
-    <t>TC_FT_PING_NEG_001</t>
-  </si>
-  <si>
     <t>Ping</t>
   </si>
   <si>
@@ -715,6 +559,180 @@
   </si>
   <si>
     <t>NOTES</t>
+  </si>
+  <si>
+    <t>1.6 Getting bookings by firstname and lastname</t>
+  </si>
+  <si>
+    <t>1. User fetches list of bookings with firstname and lastname query parameters</t>
+  </si>
+  <si>
+    <t>Response with the IDs of all the bookings filtered by "firstname" and "lastname" query parameters and OK [200] status</t>
+  </si>
+  <si>
+    <t>TC_FT_AUTH_001</t>
+  </si>
+  <si>
+    <t>TC_FT_AUTH_002</t>
+  </si>
+  <si>
+    <t>TC_FT_AUTH_003</t>
+  </si>
+  <si>
+    <t>TC_FT_AUTH_004</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_001</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_002</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_003</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_004</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_005</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_006</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_007</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_008</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_009</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_010</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_011</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_012</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_013</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_014</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_015</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_016</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_017</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_018</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_019</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_020</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_021</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_022</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_023</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_024</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_025</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_026</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_027</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_028</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_029</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_030</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_031</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_032</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_033</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_034</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_035</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_036</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_037</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_038</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_039</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_040</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_041</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_042</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_043</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_044</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_045</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_046</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_047</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_048</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_049</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_050</t>
+  </si>
+  <si>
+    <t>TC_FT_PING_001</t>
   </si>
 </sst>
 </file>
@@ -931,9 +949,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -945,6 +960,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1004,6 +1022,24 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1042,26 +1078,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1093,231 +1109,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
         <vertical style="thin">
           <color indexed="64"/>
         </vertical>
@@ -1397,6 +1188,26 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1433,6 +1244,26 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1469,6 +1300,74 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1505,6 +1404,80 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1534,6 +1507,51 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1548,19 +1566,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:K55" headerRowCount="0" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" tableBorderDxfId="10" totalsRowBorderDxfId="9" headerRowCellStyle="40% - Accent4" dataCellStyle="40% - Accent4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:K56" headerRowCount="0" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
   <tableColumns count="11">
-    <tableColumn id="12" name="Column12" headerRowDxfId="23" dataDxfId="8"/>
-    <tableColumn id="1" name="Column1" headerRowDxfId="22" dataDxfId="7"/>
-    <tableColumn id="3" name="Column4" headerRowDxfId="13" dataDxfId="6"/>
-    <tableColumn id="2" name="Column3" headerRowDxfId="21" dataDxfId="5"/>
-    <tableColumn id="4" name="Column5" headerRowDxfId="20" dataDxfId="4"/>
-    <tableColumn id="5" name="Column6" headerRowDxfId="19" dataDxfId="3"/>
-    <tableColumn id="13" name="Column2" headerRowDxfId="18"/>
-    <tableColumn id="14" name="Column11" headerRowDxfId="17"/>
-    <tableColumn id="6" name="Column7" headerRowDxfId="16" dataDxfId="2"/>
-    <tableColumn id="7" name="Column8" headerRowDxfId="15" dataDxfId="1"/>
-    <tableColumn id="9" name="Column10" headerRowDxfId="14" dataDxfId="0"/>
+    <tableColumn id="12" name="Column12" headerRowDxfId="19" dataDxfId="18"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="17" dataDxfId="16"/>
+    <tableColumn id="3" name="Column4" headerRowDxfId="15" dataDxfId="14"/>
+    <tableColumn id="2" name="Column3" headerRowDxfId="13" dataDxfId="12"/>
+    <tableColumn id="4" name="Column5" headerRowDxfId="11" dataDxfId="10"/>
+    <tableColumn id="5" name="Column6" headerRowDxfId="9" dataDxfId="8"/>
+    <tableColumn id="13" name="Column2" headerRowDxfId="7"/>
+    <tableColumn id="14" name="Column11" headerRowDxfId="6"/>
+    <tableColumn id="6" name="Column7" headerRowDxfId="5" dataDxfId="4"/>
+    <tableColumn id="7" name="Column8" headerRowDxfId="3" dataDxfId="2"/>
+    <tableColumn id="9" name="Column10" headerRowDxfId="1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1829,11 +1847,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.21875" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="23.44140625" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" customWidth="1"/>
     <col min="3" max="3" width="14.21875" customWidth="1"/>
     <col min="4" max="4" width="36.109375" customWidth="1"/>
     <col min="5" max="5" width="30.5546875" customWidth="1"/>
@@ -1846,49 +1864,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>229</v>
+      <c r="B1" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
-        <v>25</v>
+      <c r="A2" s="14" t="s">
+        <v>181</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>12</v>
@@ -1900,7 +1918,7 @@
         <v>3</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>4</v>
@@ -1916,14 +1934,14 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
-        <v>29</v>
+      <c r="A3" s="14" t="s">
+        <v>182</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>13</v>
@@ -1935,7 +1953,7 @@
         <v>5</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>4</v>
@@ -1951,14 +1969,14 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
-        <v>27</v>
+      <c r="A4" s="14" t="s">
+        <v>183</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>15</v>
@@ -1970,7 +1988,7 @@
         <v>8</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>4</v>
@@ -1986,14 +2004,14 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
-        <v>26</v>
+      <c r="A5" s="14" t="s">
+        <v>184</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>16</v>
@@ -2005,7 +2023,7 @@
         <v>17</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>4</v>
@@ -2021,14 +2039,14 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="55.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
-        <v>28</v>
+      <c r="A6" s="14" t="s">
+        <v>185</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>18</v>
@@ -2040,7 +2058,7 @@
         <v>11</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>4</v>
@@ -2056,14 +2074,14 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
-        <v>30</v>
+      <c r="A7" s="14" t="s">
+        <v>186</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>19</v>
@@ -2075,7 +2093,7 @@
         <v>20</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>4</v>
@@ -2091,14 +2109,14 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
-        <v>31</v>
+      <c r="A8" s="14" t="s">
+        <v>187</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>22</v>
@@ -2110,7 +2128,7 @@
         <v>21</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>4</v>
@@ -2126,17 +2144,17 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
-        <v>32</v>
+      <c r="A9" s="14" t="s">
+        <v>188</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>10</v>
@@ -2145,7 +2163,7 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>4</v>
@@ -2161,17 +2179,17 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="85.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
-        <v>33</v>
+      <c r="A10" s="14" t="s">
+        <v>189</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>10</v>
@@ -2180,7 +2198,7 @@
         <v>24</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>4</v>
@@ -2195,138 +2213,138 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
-        <v>36</v>
+    <row r="11" spans="1:11" ht="85.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>190</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>212</v>
+        <v>160</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>52</v>
+        <v>178</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>37</v>
+        <v>179</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>53</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="I13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>0</v>
@@ -2335,33 +2353,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
-        <v>56</v>
+    <row r="15" spans="1:11" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>194</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>4</v>
+        <v>28</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>0</v>
@@ -2371,26 +2389,26 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
-        <v>65</v>
+      <c r="A16" s="14" t="s">
+        <v>195</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>4</v>
@@ -2405,27 +2423,27 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
-        <v>55</v>
+    <row r="17" spans="1:11" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
+        <v>196</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>212</v>
+        <v>160</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>4</v>
@@ -2440,33 +2458,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
-        <v>74</v>
+    <row r="18" spans="1:11" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="14" t="s">
+        <v>197</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>0</v>
@@ -2475,33 +2493,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="10" t="s">
-        <v>79</v>
+    <row r="19" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="14" t="s">
+        <v>198</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>4</v>
+        <v>28</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>0</v>
@@ -2510,902 +2528,902 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
-        <v>68</v>
+    <row r="20" spans="1:11" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
+        <v>199</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F20" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K20" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
+      <c r="I25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="E29" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="B34" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K21" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H23" s="3" t="s">
+      <c r="E34" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="I23" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K23" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="10" t="s">
+      <c r="G34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D24" s="5" t="s">
+      <c r="I34" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="5" t="s">
+      <c r="E35" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D25" s="5" t="s">
+      <c r="I35" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E25" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="5" t="s">
+      <c r="E36" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="10" t="s">
+      <c r="E37" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D26" s="5" t="s">
+      <c r="G37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E26" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="5" t="s">
+      <c r="E38" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="56.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F41" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H28" s="3" t="s">
+      <c r="G41" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="I28" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D29" s="5" t="s">
+      <c r="H41" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D42" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E29" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F29" s="5" t="s">
+      <c r="E42" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K29" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D30" s="5" t="s">
+      <c r="E43" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E30" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H30" s="3" t="s">
+      <c r="I43" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="I30" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="10" t="s">
+      <c r="E44" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F44" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D31" s="5" t="s">
+      <c r="G44" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E31" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F31" s="5" t="s">
+      <c r="H44" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K31" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="10" t="s">
+      <c r="I44" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F45" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K33" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K35" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K37" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="56.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K38" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K39" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K40" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K41" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K42" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K43" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K44" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>178</v>
-      </c>
       <c r="G45" s="3" t="s">
-        <v>173</v>
+        <v>125</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>4</v>
@@ -3420,33 +3438,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="10" t="s">
-        <v>169</v>
+    <row r="46" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="14" t="s">
+        <v>225</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>212</v>
+        <v>160</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>174</v>
+        <v>131</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>159</v>
+        <v>129</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>0</v>
@@ -3455,33 +3473,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="10" t="s">
-        <v>179</v>
+    <row r="47" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="14" t="s">
+        <v>226</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>14</v>
+        <v>130</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>132</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>0</v>
@@ -3491,103 +3509,103 @@
       </c>
     </row>
     <row r="48" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="10" t="s">
-        <v>182</v>
+      <c r="A48" s="14" t="s">
+        <v>227</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>172</v>
+        <v>135</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>183</v>
+        <v>136</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="10" t="s">
-        <v>184</v>
+    <row r="49" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A49" s="14" t="s">
+        <v>228</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>186</v>
+        <v>138</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>172</v>
+        <v>128</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>187</v>
+        <v>137</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H49" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H50" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I49" s="4" t="s">
+      <c r="I50" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J49" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K49" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J50" s="2" t="s">
         <v>0</v>
       </c>
@@ -3595,33 +3613,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="10" t="s">
-        <v>188</v>
+    <row r="51" spans="1:11" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="14" t="s">
+        <v>230</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>212</v>
+        <v>160</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>193</v>
+        <v>141</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>194</v>
+        <v>147</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>196</v>
+        <v>142</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>0</v>
@@ -3630,33 +3648,33 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="10" t="s">
-        <v>197</v>
+    <row r="52" spans="1:11" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="14" t="s">
+        <v>231</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>14</v>
+        <v>145</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>146</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>200</v>
+        <v>148</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>0</v>
@@ -3665,108 +3683,143 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="10" t="s">
-        <v>198</v>
+    <row r="53" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A53" s="14" t="s">
+        <v>232</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>195</v>
+        <v>149</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>202</v>
+        <v>150</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="10" t="s">
-        <v>203</v>
+    <row r="54" spans="1:11" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="14" t="s">
+        <v>233</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>204</v>
+        <v>151</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>195</v>
+        <v>147</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>205</v>
+        <v>152</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H54" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H55" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I54" s="4" t="s">
+      <c r="I55" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J54" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="K54" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F55" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="J55" s="2" t="s">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="K55" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K56" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3783,25 +3836,25 @@
           <x14:formula1>
             <xm:f>Sheet1!$A$4:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I55</xm:sqref>
+          <xm:sqref>I2:I56</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet1!$A$8:$A$10</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J55</xm:sqref>
+          <xm:sqref>J2:J56</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet1!$A$13:$A$14</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C55</xm:sqref>
+          <xm:sqref>C2:C56</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Sheet1!$A$17:$A$19</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B55</xm:sqref>
+          <xm:sqref>B2:B56</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3820,12 +3873,12 @@
     <row r="2" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>217</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3836,7 +3889,7 @@
     <row r="6" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>216</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
@@ -3846,49 +3899,49 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>218</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>219</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>215</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/RESTful-booker-service-api.xlsx
+++ b/RESTful-booker-service-api.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="269">
   <si>
     <t>HIGH</t>
   </si>
@@ -816,9 +816,6 @@
     <t>TC_FT_BOOKING_054</t>
   </si>
   <si>
-    <t>1. Valid date format CCYY-MM-DD should be supported</t>
-  </si>
-  <si>
     <t>Response with new booking with nullable property "additionalneeds" and OK [200] status</t>
   </si>
   <si>
@@ -836,6 +833,12 @@
   <si>
     <t>1. User should provide valid access token
 2. A deleted booking with non-numeric ID should not exist</t>
+  </si>
+  <si>
+    <t>1. Only valid date format 'CCYY-MM-DD' should be supported</t>
+  </si>
+  <si>
+    <t>1. Only valid date with format 'CCYY-MM-DD' should be supported</t>
   </si>
 </sst>
 </file>
@@ -1134,7 +1137,177 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="241">
+  <dxfs count="128">
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="0"/>
@@ -1171,6 +1344,196 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor theme="4" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
@@ -1181,12 +1544,292 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color auto="1"/>
       </font>
       <fill>
@@ -1337,7 +1980,77 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1347,10 +2060,40 @@
     </dxf>
     <dxf>
       <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="3" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor theme="4" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
@@ -1432,1876 +2175,6 @@
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3902,19 +2775,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RESTful_booker_service_api_v1_0_0" displayName="RESTful_booker_service_api_v1_0_0" ref="A1:K63" headerRowCount="0" totalsRowShown="0" headerRowDxfId="240" dataDxfId="239" tableBorderDxfId="238" totalsRowBorderDxfId="237">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RESTful_booker_service_api_v1_0_0" displayName="RESTful_booker_service_api_v1_0_0" ref="A1:K63" headerRowCount="0" totalsRowShown="0" headerRowDxfId="127" dataDxfId="126" tableBorderDxfId="125" totalsRowBorderDxfId="124">
   <tableColumns count="11">
-    <tableColumn id="12" name="Column12" headerRowDxfId="236" dataDxfId="235"/>
-    <tableColumn id="1" name="Column1" headerRowDxfId="234" dataDxfId="233"/>
-    <tableColumn id="3" name="Column4" headerRowDxfId="232" dataDxfId="231"/>
-    <tableColumn id="2" name="Column3" headerRowDxfId="230" dataDxfId="229"/>
-    <tableColumn id="4" name="Column5" headerRowDxfId="228" dataDxfId="227"/>
-    <tableColumn id="5" name="Column6" headerRowDxfId="226" dataDxfId="225"/>
-    <tableColumn id="13" name="Column2" headerRowDxfId="224"/>
-    <tableColumn id="14" name="Column11" headerRowDxfId="223"/>
-    <tableColumn id="6" name="Column7" headerRowDxfId="222" dataDxfId="221"/>
-    <tableColumn id="7" name="Column8" headerRowDxfId="220" dataDxfId="219"/>
-    <tableColumn id="9" name="Column10" headerRowDxfId="218" dataDxfId="217"/>
+    <tableColumn id="12" name="Column12" headerRowDxfId="123" dataDxfId="122"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="121" dataDxfId="120"/>
+    <tableColumn id="3" name="Column4" headerRowDxfId="119" dataDxfId="118"/>
+    <tableColumn id="2" name="Column3" headerRowDxfId="117" dataDxfId="116"/>
+    <tableColumn id="4" name="Column5" headerRowDxfId="115" dataDxfId="114"/>
+    <tableColumn id="5" name="Column6" headerRowDxfId="113" dataDxfId="112"/>
+    <tableColumn id="13" name="Column2" headerRowDxfId="111"/>
+    <tableColumn id="14" name="Column11" headerRowDxfId="110"/>
+    <tableColumn id="6" name="Column7" headerRowDxfId="109" dataDxfId="108"/>
+    <tableColumn id="7" name="Column8" headerRowDxfId="107" dataDxfId="106"/>
+    <tableColumn id="9" name="Column10" headerRowDxfId="105" dataDxfId="104"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4843,7 +3716,7 @@
         <v>24</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="F19" s="25" t="s">
         <v>12</v>
@@ -4878,7 +3751,7 @@
         <v>23</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F20" s="25" t="s">
         <v>16</v>
@@ -4913,7 +3786,7 @@
         <v>25</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="F21" s="25" t="s">
         <v>18</v>
@@ -4948,7 +3821,7 @@
         <v>26</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F22" s="25" t="s">
         <v>19</v>
@@ -5237,7 +4110,7 @@
         <v>51</v>
       </c>
       <c r="H30" s="21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I30" s="23" t="s">
         <v>15</v>
@@ -5893,7 +4766,7 @@
         <v>97</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F49" s="25" t="s">
         <v>98</v>
@@ -5928,7 +4801,7 @@
         <v>100</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F50" s="25" t="s">
         <v>101</v>
@@ -6068,7 +4941,7 @@
         <v>109</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F54" s="25" t="s">
         <v>111</v>
@@ -6103,7 +4976,7 @@
         <v>113</v>
       </c>
       <c r="E55" s="21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F55" s="25" t="s">
         <v>114</v>
@@ -6243,7 +5116,7 @@
         <v>123</v>
       </c>
       <c r="E59" s="21" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F59" s="25" t="s">
         <v>124</v>
@@ -6278,7 +5151,7 @@
         <v>125</v>
       </c>
       <c r="E60" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F60" s="25" t="s">
         <v>126</v>
@@ -6376,8 +5249,8 @@
       <c r="B63" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="C63" s="12" t="s">
-        <v>137</v>
+      <c r="C63" s="20" t="s">
+        <v>136</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>131</v>
@@ -6414,7 +5287,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{EDFDC9AB-9D9E-41E3-BC76-B8D67636F0EA}">
+          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{EDFDC9AB-9D9E-41E3-BC76-B8D67636F0EA}">
             <xm:f>Support!$A$14</xm:f>
             <x14:dxf>
               <font>
@@ -6427,7 +5300,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{0E0E4D6F-12C1-4A01-8819-438A825BEC2D}">
+          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{0E0E4D6F-12C1-4A01-8819-438A825BEC2D}">
             <xm:f>Support!$A$13</xm:f>
             <x14:dxf>
               <font>
@@ -6443,7 +5316,7 @@
           <xm:sqref>C2:C63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="9" operator="equal" id="{E9C2B272-84B1-4809-B303-CE13207E6AB0}">
+          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{E9C2B272-84B1-4809-B303-CE13207E6AB0}">
             <xm:f>Support!$A$4</xm:f>
             <x14:dxf>
               <font>
@@ -6456,7 +5329,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="10" operator="equal" id="{E67A97B1-A6AA-4AEA-841E-887676001F2D}">
+          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{E67A97B1-A6AA-4AEA-841E-887676001F2D}">
             <xm:f>Support!$A$5</xm:f>
             <x14:dxf>
               <font>
@@ -6470,51 +5343,6 @@
             </x14:dxf>
           </x14:cfRule>
           <xm:sqref>I2:I63</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{45F6DB1C-4FF9-49E6-9475-597C87185476}">
-            <xm:f>Support!$A$17</xm:f>
-            <x14:dxf>
-              <font>
-                <color auto="1"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="3" tint="0.59996337778862885"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{C74CA95C-7727-418A-BE78-990F3D7CE068}">
-            <xm:f>Support!$A$18</xm:f>
-            <x14:dxf>
-              <font>
-                <color auto="1"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="7" tint="0.59996337778862885"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:B63</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{3EE337D8-8BAD-4B99-8E46-C9C511026EE5}">
-            <xm:f>Support!$A$19</xm:f>
-            <x14:dxf>
-              <font>
-                <color auto="1"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="4" tint="0.59996337778862885"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="3" operator="equal" id="{9540FE2F-D658-42C7-87B5-25E1482BD07B}">
@@ -6557,6 +5385,48 @@
             </x14:dxf>
           </x14:cfRule>
           <xm:sqref>J2:J63</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="8" id="{C74CA95C-7727-418A-BE78-990F3D7CE068}">
+            <xm:f>$B2=+Support!$A$18</xm:f>
+            <x14:dxf>
+              <font>
+                <color auto="1"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="7" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="9" id="{45F6DB1C-4FF9-49E6-9475-597C87185476}">
+            <xm:f>$B2=Support!$A$17</xm:f>
+            <x14:dxf>
+              <font>
+                <color auto="1"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="3" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="10" id="{3EE337D8-8BAD-4B99-8E46-C9C511026EE5}">
+            <xm:f>$B1048517=Support!$A$19</xm:f>
+            <x14:dxf>
+              <font>
+                <color auto="1"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="4" tint="0.79998168889431442"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A2:K63</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/RESTful-booker-service-api.xlsx
+++ b/RESTful-booker-service-api.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="281">
   <si>
     <t>HIGH</t>
   </si>
@@ -60,12 +60,6 @@
     <t>1.4 Getting list of bookings after checkin date</t>
   </si>
   <si>
-    <t>1.5 Getting list of bookings after checkout date</t>
-  </si>
-  <si>
-    <t>1. User fetches list of bookings with invalid checkin date</t>
-  </si>
-  <si>
     <t>Response with Bad Request [400] status and error message</t>
   </si>
   <si>
@@ -75,18 +69,9 @@
     <t>FAIL</t>
   </si>
   <si>
-    <t>1. User fetches list of bookings with invalid checkin date format</t>
-  </si>
-  <si>
     <t>Response with the IDs of all the bookings after the specified checkin date with invalid format and OK [200] status</t>
   </si>
   <si>
-    <t>1. User fetches list of bookings with invalid checkout date</t>
-  </si>
-  <si>
-    <t>1. User fetches list of bookings with invalid checkout date format</t>
-  </si>
-  <si>
     <t>Response with the IDs of all the bookings after the specified checkout date with invalid format and OK [200] status</t>
   </si>
   <si>
@@ -96,18 +81,6 @@
     <t>CRITICAL</t>
   </si>
   <si>
-    <t>1.2 Getting bookings by invalid checkin date format</t>
-  </si>
-  <si>
-    <t>1.1 Getting bookings by invalid checkin date</t>
-  </si>
-  <si>
-    <t>1.3 Getting bookings by invalid checkout date</t>
-  </si>
-  <si>
-    <t>1.4 Getting bookings by invalid checkout date format</t>
-  </si>
-  <si>
     <t>1. User fetches booking by ID</t>
   </si>
   <si>
@@ -151,9 +124,6 @@
   </si>
   <si>
     <t>1. User fetches booking by non-numeric ID</t>
-  </si>
-  <si>
-    <t>Response with the IDs of all the bookings filtered after booking "checkout" date query parameter with OK [200] status</t>
   </si>
   <si>
     <t>3.1 Create new booking</t>
@@ -839,6 +809,72 @@
   </si>
   <si>
     <t>1. Only valid date with format 'CCYY-MM-DD' should be supported</t>
+  </si>
+  <si>
+    <t>1.1 Getting bookings by non-existing checkin date</t>
+  </si>
+  <si>
+    <t>1.2 Getting bookings by invalid checkin date</t>
+  </si>
+  <si>
+    <t>1.3 Getting bookings by invalid checkin date format (YYYY)</t>
+  </si>
+  <si>
+    <t>1.4 Getting bookings by max checkin date</t>
+  </si>
+  <si>
+    <t>1. User fetches list of bookings by max checkin date</t>
+  </si>
+  <si>
+    <t>1.5 Getting bookings by non-existing checkout date</t>
+  </si>
+  <si>
+    <t>1.6 Getting bookings by invalid checkout date</t>
+  </si>
+  <si>
+    <t>1.7 Getting bookings by invalid checkout date format (YYYY)</t>
+  </si>
+  <si>
+    <t>1.8 Getting bookings by min checkout date</t>
+  </si>
+  <si>
+    <t>1. User fetches list of bookings by non-existing checkin date</t>
+  </si>
+  <si>
+    <t>1. User fetches list of bookings by invalid checkin date</t>
+  </si>
+  <si>
+    <t>1. User fetches list of bookings by invalid checkin date format</t>
+  </si>
+  <si>
+    <t>1. User fetches list of bookings by non-existing checkout date</t>
+  </si>
+  <si>
+    <t>1. User fetches list of bookings by invalid checkout date</t>
+  </si>
+  <si>
+    <t>1. User fetches list of bookings by invalid checkout date format</t>
+  </si>
+  <si>
+    <t>1. User fetches list of bookings by min checkout date format</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_055</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_056</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_057</t>
+  </si>
+  <si>
+    <t>TC_FT_BOOKING_058</t>
+  </si>
+  <si>
+    <t>1.5 Getting list of bookings before checkout date</t>
+  </si>
+  <si>
+    <t>Response with the IDs of all the bookings filtered before booking "checkout" date query parameter with OK [200] status</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1086,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -1133,11 +1169,14 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="128">
+  <dxfs count="272">
     <dxf>
       <font>
         <color auto="1"/>
@@ -1170,6 +1209,76 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color auto="1"/>
       </font>
       <fill>
@@ -1200,941 +1309,31 @@
     </dxf>
     <dxf>
       <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color theme="0"/>
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor theme="3" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2213,24 +1412,6 @@
           <color indexed="64"/>
         </horizontal>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2287,6 +1468,26 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2343,42 +1544,26 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2434,7 +1619,55 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2475,248 +1708,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <border>
         <top style="thin">
           <color indexed="64"/>
@@ -2761,6 +1752,2494 @@
         </horizontal>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2775,19 +4254,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RESTful_booker_service_api_v1_0_0" displayName="RESTful_booker_service_api_v1_0_0" ref="A1:K63" headerRowCount="0" totalsRowShown="0" headerRowDxfId="127" dataDxfId="126" tableBorderDxfId="125" totalsRowBorderDxfId="124">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RESTful_booker_service_api_v1_0_0" displayName="RESTful_booker_service_api_v1_0_0" ref="A1:K67" headerRowCount="0" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" tableBorderDxfId="30" totalsRowBorderDxfId="29" headerRowCellStyle="60% - Accent1" dataCellStyle="60% - Accent1">
   <tableColumns count="11">
-    <tableColumn id="12" name="Column12" headerRowDxfId="123" dataDxfId="122"/>
-    <tableColumn id="1" name="Column1" headerRowDxfId="121" dataDxfId="120"/>
-    <tableColumn id="3" name="Column4" headerRowDxfId="119" dataDxfId="118"/>
-    <tableColumn id="2" name="Column3" headerRowDxfId="117" dataDxfId="116"/>
-    <tableColumn id="4" name="Column5" headerRowDxfId="115" dataDxfId="114"/>
-    <tableColumn id="5" name="Column6" headerRowDxfId="113" dataDxfId="112"/>
-    <tableColumn id="13" name="Column2" headerRowDxfId="111"/>
-    <tableColumn id="14" name="Column11" headerRowDxfId="110"/>
-    <tableColumn id="6" name="Column7" headerRowDxfId="109" dataDxfId="108"/>
-    <tableColumn id="7" name="Column8" headerRowDxfId="107" dataDxfId="106"/>
-    <tableColumn id="9" name="Column10" headerRowDxfId="105" dataDxfId="104"/>
+    <tableColumn id="12" name="Column12" headerRowDxfId="271" dataDxfId="28"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="270" dataDxfId="27"/>
+    <tableColumn id="3" name="Column4" headerRowDxfId="269" dataDxfId="26"/>
+    <tableColumn id="2" name="Column3" headerRowDxfId="268" dataDxfId="25"/>
+    <tableColumn id="4" name="Column5" headerRowDxfId="267" dataDxfId="24"/>
+    <tableColumn id="5" name="Column6" headerRowDxfId="266" dataDxfId="23"/>
+    <tableColumn id="13" name="Column2" headerRowDxfId="265"/>
+    <tableColumn id="14" name="Column11" headerRowDxfId="264"/>
+    <tableColumn id="6" name="Column7" headerRowDxfId="263" dataDxfId="22"/>
+    <tableColumn id="7" name="Column8" headerRowDxfId="262" dataDxfId="21"/>
+    <tableColumn id="9" name="Column10" headerRowDxfId="261" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3056,16 +4535,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.44140625" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.44140625" customWidth="1"/>
     <col min="4" max="4" width="36.109375" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="45.109375" customWidth="1"/>
-    <col min="7" max="7" width="29.44140625" customWidth="1"/>
+    <col min="7" max="7" width="35.44140625" customWidth="1"/>
     <col min="8" max="8" width="37" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="10" width="21.77734375" customWidth="1"/>
@@ -3077,57 +4556,57 @@
         <v>1</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="I1" s="28" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="J1" s="28" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="K1" s="29" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>5</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>3</v>
@@ -3144,25 +4623,25 @@
     </row>
     <row r="3" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>3</v>
@@ -3179,25 +4658,25 @@
     </row>
     <row r="4" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>3</v>
@@ -3214,25 +4693,25 @@
     </row>
     <row r="5" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>3</v>
@@ -3249,25 +4728,25 @@
     </row>
     <row r="6" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>3</v>
@@ -3284,25 +4763,25 @@
     </row>
     <row r="7" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>3</v>
@@ -3319,25 +4798,25 @@
     </row>
     <row r="8" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>3</v>
@@ -3354,25 +4833,25 @@
     </row>
     <row r="9" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D9" s="25" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F9" s="25" t="s">
         <v>4</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H9" s="22" t="s">
         <v>3</v>
@@ -3387,27 +4866,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H10" s="22" t="s">
         <v>3</v>
@@ -3422,27 +4901,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H11" s="22" t="s">
         <v>3</v>
@@ -3457,27 +4936,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H12" s="22" t="s">
         <v>3</v>
@@ -3492,27 +4971,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B13" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="F13" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="C13" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>244</v>
-      </c>
       <c r="G13" s="21" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H13" s="22" t="s">
         <v>3</v>
@@ -3527,27 +5006,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D14" s="25" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F14" s="25" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H14" s="22" t="s">
         <v>3</v>
@@ -3562,27 +5041,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>11</v>
+        <v>279</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F15" s="25" t="s">
         <v>9</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>42</v>
+        <v>280</v>
       </c>
       <c r="H15" s="22" t="s">
         <v>3</v>
@@ -3597,27 +5076,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H16" s="22" t="s">
         <v>3</v>
@@ -3632,27 +5111,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H17" s="22" t="s">
         <v>3</v>
@@ -3667,27 +5146,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H18" s="22" t="s">
         <v>3</v>
@@ -3702,138 +5181,136 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>24</v>
+        <v>259</v>
       </c>
       <c r="E19" s="25" t="s">
+        <v>258</v>
+      </c>
+      <c r="F19" s="25" t="s">
         <v>268</v>
       </c>
-      <c r="F19" s="25" t="s">
+      <c r="G19" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="21" t="s">
+      <c r="I19" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="23" t="s">
-        <v>15</v>
-      </c>
       <c r="J19" s="22" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K19" s="24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>23</v>
+        <v>260</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>16</v>
+        <v>269</v>
       </c>
       <c r="G20" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="H20" s="21" t="s">
+      <c r="J20" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="K20" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K20" s="30"/>
+    </row>
+    <row r="21" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>25</v>
+        <v>261</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>18</v>
+        <v>270</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H21" s="21" t="s">
         <v>14</v>
       </c>
       <c r="I21" s="23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K21" s="24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>26</v>
+        <v>262</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>19</v>
+        <v>263</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" s="21" t="s">
-        <v>20</v>
+        <v>230</v>
+      </c>
+      <c r="H22" s="22" t="s">
+        <v>3</v>
       </c>
       <c r="I22" s="23" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J22" s="22" t="s">
         <v>0</v>
@@ -3842,103 +5319,103 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>36</v>
+        <v>264</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>210</v>
+        <v>258</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>27</v>
+        <v>271</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="H23" s="22" t="s">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>12</v>
       </c>
       <c r="I23" s="23" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K23" s="24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>37</v>
+        <v>265</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>210</v>
+        <v>258</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>35</v>
+        <v>272</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="H24" s="22" t="s">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>12</v>
       </c>
       <c r="I24" s="23" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J24" s="22" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K24" s="24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>38</v>
+        <v>273</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="H25" s="22" t="s">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="H25" s="21" t="s">
+        <v>15</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J25" s="22" t="s">
         <v>0</v>
@@ -3947,33 +5424,33 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>41</v>
+        <v>274</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26" s="21" t="s">
-        <v>40</v>
+        <v>230</v>
+      </c>
+      <c r="H26" s="22" t="s">
+        <v>3</v>
       </c>
       <c r="I26" s="23" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J26" s="22" t="s">
         <v>0</v>
@@ -3982,27 +5459,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>256</v>
+        <v>27</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H27" s="22" t="s">
         <v>3</v>
@@ -4017,33 +5494,33 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>257</v>
+        <v>28</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="G28" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="H28" s="21" t="s">
-        <v>40</v>
+        <v>25</v>
+      </c>
+      <c r="H28" s="22" t="s">
+        <v>3</v>
       </c>
       <c r="I28" s="23" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J28" s="22" t="s">
         <v>0</v>
@@ -4052,348 +5529,348 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D29" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="F29" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="K29" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="F30" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="K30" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="F31" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="H31" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="I31" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="K31" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>247</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="F32" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J32" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="K32" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F33" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="G33" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H33" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I33" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K33" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F34" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="H34" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="I34" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K34" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F35" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="H35" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" s="25" t="s">
+      <c r="I35" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K35" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="D36" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="G29" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="H29" s="21" t="s">
+      <c r="E36" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="I29" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K29" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="D30" s="25" t="s">
+      <c r="G36" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" s="25" t="s">
+      <c r="H36" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="21" t="s">
+      <c r="I36" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K36" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F37" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H37" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I37" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J37" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="H30" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="I30" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K30" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="D31" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E31" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="G31" s="21" t="s">
+      <c r="E38" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F38" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G38" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H38" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="H31" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="I31" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K31" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="D32" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="E32" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="G32" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="H32" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="I32" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K32" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="E33" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="G33" s="21" t="s">
+      <c r="I38" s="23" t="s">
         <v>13</v>
-      </c>
-      <c r="H33" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J33" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="K33" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D34" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="E34" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="G34" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="H34" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="I34" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="K34" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="B35" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D35" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="E35" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="G35" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="H35" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="K35" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="E36" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G36" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="H36" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="I36" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J36" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="K36" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D37" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="E37" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="G37" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="H37" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I37" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J37" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="K37" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D38" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="E38" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="G38" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="H38" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="I38" s="23" t="s">
-        <v>15</v>
       </c>
       <c r="J38" s="22" t="s">
         <v>0</v>
@@ -4402,138 +5879,138 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="19" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="E39" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="G39" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I39" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="H39" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I39" s="23" t="s">
-        <v>15</v>
-      </c>
       <c r="J39" s="22" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K39" s="24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="19" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="E40" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="G40" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="I40" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="H40" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I40" s="23" t="s">
-        <v>15</v>
-      </c>
       <c r="J40" s="22" t="s">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K40" s="24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="19" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E41" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="G41" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I41" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="H41" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="I41" s="23" t="s">
-        <v>15</v>
-      </c>
       <c r="J41" s="22" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K41" s="24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="19" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="E42" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="G42" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="I42" s="23" t="s">
         <v>13</v>
-      </c>
-      <c r="H42" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="I42" s="23" t="s">
-        <v>15</v>
       </c>
       <c r="J42" s="22" t="s">
         <v>0</v>
@@ -4542,103 +6019,103 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="19" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D43" s="25" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="E43" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F43" s="25" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="G43" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I43" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="H43" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I43" s="23" t="s">
-        <v>15</v>
-      </c>
       <c r="J43" s="22" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K43" s="24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="19" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E44" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="G44" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I44" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="H44" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I44" s="23" t="s">
-        <v>15</v>
-      </c>
       <c r="J44" s="22" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K44" s="24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="19" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="E45" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="G45" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="I45" s="23" t="s">
         <v>13</v>
-      </c>
-      <c r="H45" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="I45" s="23" t="s">
-        <v>15</v>
       </c>
       <c r="J45" s="22" t="s">
         <v>0</v>
@@ -4647,138 +6124,138 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="19" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="E46" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="G46" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I46" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="H46" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I46" s="23" t="s">
-        <v>15</v>
-      </c>
       <c r="J46" s="22" t="s">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K46" s="24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="19" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D47" s="25" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="E47" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="G47" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I47" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="H47" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I47" s="23" t="s">
-        <v>15</v>
-      </c>
       <c r="J47" s="22" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K47" s="24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="19" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="E48" s="21" t="s">
-        <v>207</v>
+        <v>75</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>6</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="G48" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="H48" s="22" t="s">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="H48" s="21" t="s">
+        <v>12</v>
       </c>
       <c r="I48" s="23" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J48" s="22" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K48" s="24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="19" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D49" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="E49" s="21" t="s">
-        <v>263</v>
+        <v>79</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>6</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="G49" s="21" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H49" s="21" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="I49" s="23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J49" s="22" t="s">
         <v>0</v>
@@ -4787,97 +6264,97 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D50" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E50" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F50" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="G50" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I50" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="K50" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C51" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D51" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="E51" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F51" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="G51" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H51" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I51" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J51" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="K51" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="E52" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="B50" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D50" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="E50" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="F50" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="G50" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="H50" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="I50" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J50" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="K50" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="B51" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C51" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D51" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="E51" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F51" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="G51" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="H51" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="I51" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J51" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K51" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="B52" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C52" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D52" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="E52" s="26" t="s">
-        <v>6</v>
-      </c>
       <c r="F52" s="25" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="G52" s="21" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="H52" s="22" t="s">
         <v>3</v>
@@ -4892,33 +6369,33 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="19" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D53" s="25" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="E53" s="21" t="s">
-        <v>208</v>
+        <v>253</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="G53" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="H53" s="22" t="s">
-        <v>3</v>
+        <v>30</v>
+      </c>
+      <c r="H53" s="21" t="s">
+        <v>89</v>
       </c>
       <c r="I53" s="23" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J53" s="22" t="s">
         <v>0</v>
@@ -4927,33 +6404,33 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="19" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="G54" s="21" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="H54" s="21" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="I54" s="23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J54" s="22" t="s">
         <v>0</v>
@@ -4962,97 +6439,97 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="19" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D55" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="E55" s="21" t="s">
-        <v>264</v>
+        <v>92</v>
+      </c>
+      <c r="E55" s="26" t="s">
+        <v>6</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="G55" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="H55" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="I55" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="H55" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="I55" s="23" t="s">
-        <v>15</v>
-      </c>
       <c r="J55" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K55" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D56" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="E56" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F56" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="G56" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H56" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="I56" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="J56" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="K55" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="B56" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C56" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D56" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="E56" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="G56" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="H56" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="I56" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J56" s="22" t="s">
-        <v>21</v>
-      </c>
       <c r="K56" s="24" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="19" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D57" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="E57" s="26" t="s">
-        <v>6</v>
+        <v>100</v>
+      </c>
+      <c r="E57" s="21" t="s">
+        <v>198</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="G57" s="21" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="H57" s="22" t="s">
         <v>3</v>
@@ -5067,33 +6544,33 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="19" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D58" s="25" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>209</v>
+        <v>253</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="G58" s="21" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="H58" s="21" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="I58" s="23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J58" s="22" t="s">
         <v>0</v>
@@ -5102,33 +6579,33 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="19" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D59" s="25" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="E59" s="21" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="G59" s="21" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="H59" s="21" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="I59" s="23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J59" s="22" t="s">
         <v>0</v>
@@ -5137,103 +6614,103 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="19" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="E60" s="21" t="s">
-        <v>266</v>
+        <v>106</v>
+      </c>
+      <c r="E60" s="26" t="s">
+        <v>6</v>
       </c>
       <c r="F60" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="G60" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="H60" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="I60" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J60" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K60" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D61" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="E61" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F61" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="G61" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H61" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="I61" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="J61" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="K61" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C62" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="G60" s="21" t="s">
+      <c r="D62" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="E62" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="F62" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="G62" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="H62" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="I62" s="23" t="s">
         <v>13</v>
-      </c>
-      <c r="H60" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="I60" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J60" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="K60" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="B61" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C61" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D61" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="E61" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="G61" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="H61" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="I61" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J61" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K61" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="B62" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="C62" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D62" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="E62" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F62" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="G62" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="H62" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="23" t="s">
-        <v>2</v>
       </c>
       <c r="J62" s="22" t="s">
         <v>0</v>
@@ -5242,38 +6719,178 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>235</v>
+    <row r="63" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>224</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="E63" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="G63" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="H63" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="I63" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="J63" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="K63" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D63" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="E63" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="F63" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G63" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="H63" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="I63" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J63" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="K63" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C64" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D64" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="E64" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="F64" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="G64" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H64" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="I64" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J64" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="K64" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C65" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D65" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E65" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F65" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="G65" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="H65" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="I65" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J65" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K65" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="B66" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C66" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D66" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E66" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F66" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="G66" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H66" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="J66" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="K66" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C67" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E67" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F67" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G67" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="H67" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="I67" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K67" s="18" t="s">
         <v>6</v>
       </c>
     </row>
@@ -5287,7 +6904,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{EDFDC9AB-9D9E-41E3-BC76-B8D67636F0EA}">
+          <x14:cfRule type="cellIs" priority="40" operator="equal" id="{EDFDC9AB-9D9E-41E3-BC76-B8D67636F0EA}">
             <xm:f>Support!$A$14</xm:f>
             <x14:dxf>
               <font>
@@ -5300,7 +6917,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{0E0E4D6F-12C1-4A01-8819-438A825BEC2D}">
+          <x14:cfRule type="cellIs" priority="41" operator="equal" id="{0E0E4D6F-12C1-4A01-8819-438A825BEC2D}">
             <xm:f>Support!$A$13</xm:f>
             <x14:dxf>
               <font>
@@ -5313,10 +6930,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>C2:C63</xm:sqref>
+          <xm:sqref>C2:C67</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{E9C2B272-84B1-4809-B303-CE13207E6AB0}">
+          <x14:cfRule type="cellIs" priority="42" operator="equal" id="{E9C2B272-84B1-4809-B303-CE13207E6AB0}">
             <xm:f>Support!$A$4</xm:f>
             <x14:dxf>
               <font>
@@ -5329,7 +6946,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{E67A97B1-A6AA-4AEA-841E-887676001F2D}">
+          <x14:cfRule type="cellIs" priority="43" operator="equal" id="{E67A97B1-A6AA-4AEA-841E-887676001F2D}">
             <xm:f>Support!$A$5</xm:f>
             <x14:dxf>
               <font>
@@ -5342,10 +6959,36 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>I2:I63</xm:sqref>
+          <xm:sqref>I2:I67</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{9540FE2F-D658-42C7-87B5-25E1482BD07B}">
+          <x14:cfRule type="cellIs" priority="37" operator="equal" id="{6B56C5F3-9AF3-4BD5-87CE-CADFFFDFA65E}">
+            <xm:f>Support!$A$10</xm:f>
+            <x14:dxf>
+              <font>
+                <color theme="0"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="3" tint="-0.24994659260841701"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="38" operator="equal" id="{40213F7A-A98A-41D2-B624-532374AC6E4B}">
+            <xm:f>Support!$A$9</xm:f>
+            <x14:dxf>
+              <font>
+                <color theme="0"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor theme="4" tint="-0.24994659260841701"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="39" operator="equal" id="{9540FE2F-D658-42C7-87B5-25E1482BD07B}">
             <xm:f>Support!$A$8</xm:f>
             <x14:dxf>
               <font>
@@ -5358,36 +7001,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{40213F7A-A98A-41D2-B624-532374AC6E4B}">
-            <xm:f>Support!$A$9</xm:f>
-            <x14:dxf>
-              <font>
-                <color theme="0"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="4" tint="-0.24994659260841701"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{6B56C5F3-9AF3-4BD5-87CE-CADFFFDFA65E}">
-            <xm:f>Support!$A$10</xm:f>
-            <x14:dxf>
-              <font>
-                <color theme="0"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor theme="3" tint="-0.24994659260841701"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>J2:J63</xm:sqref>
+          <xm:sqref>J2:J67</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="8" id="{C74CA95C-7727-418A-BE78-990F3D7CE068}">
+          <x14:cfRule type="expression" priority="77" id="{C74CA95C-7727-418A-BE78-990F3D7CE068}">
             <xm:f>$B2=+Support!$A$18</xm:f>
             <x14:dxf>
               <font>
@@ -5400,7 +7017,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="9" id="{45F6DB1C-4FF9-49E6-9475-597C87185476}">
+          <x14:cfRule type="expression" priority="78" id="{45F6DB1C-4FF9-49E6-9475-597C87185476}">
             <xm:f>$B2=Support!$A$17</xm:f>
             <x14:dxf>
               <font>
@@ -5413,8 +7030,8 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="10" id="{3EE337D8-8BAD-4B99-8E46-C9C511026EE5}">
-            <xm:f>$B1048517=Support!$A$19</xm:f>
+          <x14:cfRule type="expression" priority="79" id="{3EE337D8-8BAD-4B99-8E46-C9C511026EE5}">
+            <xm:f>$B2=Support!$A$19</xm:f>
             <x14:dxf>
               <font>
                 <color auto="1"/>
@@ -5426,7 +7043,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A2:K63</xm:sqref>
+          <xm:sqref>A2:K67</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -5436,25 +7053,25 @@
           <x14:formula1>
             <xm:f>Support!$A$4:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I63</xm:sqref>
+          <xm:sqref>I2:I67</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Support!$A$8:$A$10</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J63</xm:sqref>
+          <xm:sqref>J2:J67</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Support!$A$13:$A$14</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C63</xm:sqref>
+          <xm:sqref>C2:C67</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Support!$A$17:$A$19</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B63</xm:sqref>
+          <xm:sqref>B2:B67</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5473,12 +7090,12 @@
     <row r="2" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5489,7 +7106,7 @@
     <row r="6" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
@@ -5499,49 +7116,49 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/RESTful-booker-service-api.xlsx
+++ b/RESTful-booker-service-api.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="284">
   <si>
     <t>HIGH</t>
   </si>
@@ -633,9 +633,6 @@
     <t>1. Not empty bookings list should exist</t>
   </si>
   <si>
-    <t>1. A user with empty username/password should not exist</t>
-  </si>
-  <si>
     <t>1. A user with valid username/password should exist</t>
   </si>
   <si>
@@ -875,6 +872,18 @@
   </si>
   <si>
     <t>Response with the IDs of all the bookings filtered before booking "checkout" date query parameter with OK [200] status</t>
+  </si>
+  <si>
+    <t>TC_FT_AUTH_008</t>
+  </si>
+  <si>
+    <t>1.7 Creating new token with empty body</t>
+  </si>
+  <si>
+    <t>1. A user with empty username and password should not exist</t>
+  </si>
+  <si>
+    <t>1. User provides empty body</t>
   </si>
 </sst>
 </file>
@@ -1176,7 +1185,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="272">
+  <dxfs count="77">
     <dxf>
       <font>
         <color auto="1"/>
@@ -1209,6 +1218,36 @@
     </dxf>
     <dxf>
       <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -1243,6 +1282,36 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
@@ -1263,6 +1332,216 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -1274,6 +1553,66 @@
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1430,26 +1769,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1506,26 +1825,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1582,26 +1881,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1619,19 +1898,7 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1650,24 +1917,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1708,2331 +1957,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -4067,6 +1991,26 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -4103,6 +2047,26 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -4138,7 +2102,19 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -4175,6 +2151,24 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -4211,6 +2205,26 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -4238,6 +2252,51 @@
         </right>
         <top/>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
   </dxfs>
@@ -4254,19 +2313,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RESTful_booker_service_api_v1_0_0" displayName="RESTful_booker_service_api_v1_0_0" ref="A1:K67" headerRowCount="0" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" tableBorderDxfId="30" totalsRowBorderDxfId="29" headerRowCellStyle="60% - Accent1" dataCellStyle="60% - Accent1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RESTful_booker_service_api_v1_0_0" displayName="RESTful_booker_service_api_v1_0_0" ref="A1:K68" headerRowCount="0" totalsRowShown="0" headerRowDxfId="76" dataDxfId="75" tableBorderDxfId="74" totalsRowBorderDxfId="73">
   <tableColumns count="11">
-    <tableColumn id="12" name="Column12" headerRowDxfId="271" dataDxfId="28"/>
-    <tableColumn id="1" name="Column1" headerRowDxfId="270" dataDxfId="27"/>
-    <tableColumn id="3" name="Column4" headerRowDxfId="269" dataDxfId="26"/>
-    <tableColumn id="2" name="Column3" headerRowDxfId="268" dataDxfId="25"/>
-    <tableColumn id="4" name="Column5" headerRowDxfId="267" dataDxfId="24"/>
-    <tableColumn id="5" name="Column6" headerRowDxfId="266" dataDxfId="23"/>
-    <tableColumn id="13" name="Column2" headerRowDxfId="265"/>
-    <tableColumn id="14" name="Column11" headerRowDxfId="264"/>
-    <tableColumn id="6" name="Column7" headerRowDxfId="263" dataDxfId="22"/>
-    <tableColumn id="7" name="Column8" headerRowDxfId="262" dataDxfId="21"/>
-    <tableColumn id="9" name="Column10" headerRowDxfId="261" dataDxfId="20"/>
+    <tableColumn id="12" name="Column12" headerRowDxfId="72" dataDxfId="71"/>
+    <tableColumn id="1" name="Column1" headerRowDxfId="70" dataDxfId="69"/>
+    <tableColumn id="3" name="Column4" headerRowDxfId="68" dataDxfId="67"/>
+    <tableColumn id="2" name="Column3" headerRowDxfId="66" dataDxfId="65"/>
+    <tableColumn id="4" name="Column5" headerRowDxfId="64" dataDxfId="63"/>
+    <tableColumn id="5" name="Column6" headerRowDxfId="62" dataDxfId="61"/>
+    <tableColumn id="13" name="Column2" headerRowDxfId="60"/>
+    <tableColumn id="14" name="Column11" headerRowDxfId="59"/>
+    <tableColumn id="6" name="Column7" headerRowDxfId="58" dataDxfId="57"/>
+    <tableColumn id="7" name="Column8" headerRowDxfId="56" dataDxfId="55"/>
+    <tableColumn id="9" name="Column10" headerRowDxfId="54" dataDxfId="53"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4535,7 +2594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.44140625" customWidth="1"/>
@@ -4591,7 +2650,7 @@
         <v>142</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>126</v>
@@ -4600,10 +2659,10 @@
         <v>5</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>24</v>
@@ -4626,19 +2685,19 @@
         <v>143</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>127</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>23</v>
@@ -4661,19 +2720,19 @@
         <v>144</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>127</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>201</v>
+        <v>282</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>23</v>
@@ -4696,19 +2755,19 @@
         <v>145</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>127</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>23</v>
@@ -4728,22 +2787,22 @@
     </row>
     <row r="6" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>127</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>23</v>
@@ -4763,22 +2822,22 @@
     </row>
     <row r="7" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>127</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="6" t="s">
         <v>217</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>218</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>23</v>
@@ -4798,22 +2857,22 @@
     </row>
     <row r="8" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>127</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>221</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>222</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>23</v>
@@ -4832,61 +2891,61 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="J9" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="K9" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
-        <v>147</v>
-      </c>
       <c r="B10" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>126</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>226</v>
+        <v>7</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>200</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>229</v>
+        <v>4</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H10" s="22" t="s">
         <v>3</v>
@@ -4903,16 +2962,16 @@
     </row>
     <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>126</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>200</v>
@@ -4921,7 +2980,7 @@
         <v>228</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="H11" s="22" t="s">
         <v>3</v>
@@ -4938,25 +2997,25 @@
     </row>
     <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>126</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>200</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="H12" s="22" t="s">
         <v>3</v>
@@ -4973,25 +3032,25 @@
     </row>
     <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>126</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>200</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>230</v>
+        <v>20</v>
       </c>
       <c r="H13" s="22" t="s">
         <v>3</v>
@@ -5008,25 +3067,25 @@
     </row>
     <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>126</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>10</v>
+        <v>232</v>
       </c>
       <c r="E14" s="25" t="s">
         <v>200</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>8</v>
+        <v>233</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>19</v>
+        <v>229</v>
       </c>
       <c r="H14" s="22" t="s">
         <v>3</v>
@@ -5043,25 +3102,25 @@
     </row>
     <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>126</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>279</v>
+        <v>10</v>
       </c>
       <c r="E15" s="25" t="s">
         <v>200</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>280</v>
+        <v>19</v>
       </c>
       <c r="H15" s="22" t="s">
         <v>3</v>
@@ -5078,25 +3137,25 @@
     </row>
     <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>126</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="E16" s="25" t="s">
         <v>200</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>235</v>
+        <v>9</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>141</v>
+        <v>279</v>
       </c>
       <c r="H16" s="22" t="s">
         <v>3</v>
@@ -5113,25 +3172,25 @@
     </row>
     <row r="17" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>126</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E17" s="25" t="s">
         <v>200</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>230</v>
+        <v>141</v>
       </c>
       <c r="H17" s="22" t="s">
         <v>3</v>
@@ -5148,25 +3207,25 @@
     </row>
     <row r="18" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>126</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E18" s="25" t="s">
         <v>200</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H18" s="22" t="s">
         <v>3</v>
@@ -5183,34 +3242,34 @@
     </row>
     <row r="19" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>258</v>
+        <v>200</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>268</v>
+        <v>239</v>
       </c>
       <c r="G19" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="H19" s="21" t="s">
-        <v>12</v>
+        <v>229</v>
+      </c>
+      <c r="H19" s="22" t="s">
+        <v>3</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K19" s="24" t="s">
         <v>6</v>
@@ -5218,22 +3277,22 @@
     </row>
     <row r="20" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G20" s="21" t="s">
         <v>11</v>
@@ -5247,70 +3306,70 @@
       <c r="J20" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="K20" s="30"/>
+      <c r="K20" s="24" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="21" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E21" s="25" t="s">
         <v>257</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G21" s="21" t="s">
         <v>11</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I21" s="23" t="s">
         <v>13</v>
       </c>
       <c r="J21" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="K21" s="24" t="s">
-        <v>6</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="K21" s="30"/>
     </row>
     <row r="22" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="H22" s="22" t="s">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="H22" s="21" t="s">
+        <v>14</v>
       </c>
       <c r="I22" s="23" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J22" s="22" t="s">
         <v>0</v>
@@ -5321,34 +3380,34 @@
     </row>
     <row r="23" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="H23" s="21" t="s">
-        <v>12</v>
+        <v>229</v>
+      </c>
+      <c r="H23" s="22" t="s">
+        <v>3</v>
       </c>
       <c r="I23" s="23" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J23" s="22" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K23" s="24" t="s">
         <v>6</v>
@@ -5356,22 +3415,22 @@
     </row>
     <row r="24" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C24" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G24" s="21" t="s">
         <v>11</v>
@@ -5391,34 +3450,34 @@
     </row>
     <row r="25" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E25" s="25" t="s">
         <v>257</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G25" s="21" t="s">
         <v>11</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I25" s="23" t="s">
         <v>13</v>
       </c>
       <c r="J25" s="22" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K25" s="24" t="s">
         <v>6</v>
@@ -5426,31 +3485,31 @@
     </row>
     <row r="26" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="H26" s="22" t="s">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>15</v>
       </c>
       <c r="I26" s="23" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J26" s="22" t="s">
         <v>0</v>
@@ -5461,25 +3520,25 @@
     </row>
     <row r="27" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>27</v>
+        <v>266</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>200</v>
+        <v>256</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>18</v>
+        <v>273</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>25</v>
+        <v>229</v>
       </c>
       <c r="H27" s="22" t="s">
         <v>3</v>
@@ -5496,22 +3555,22 @@
     </row>
     <row r="28" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C28" s="20" t="s">
         <v>126</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E28" s="25" t="s">
         <v>200</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G28" s="21" t="s">
         <v>25</v>
@@ -5531,25 +3590,25 @@
     </row>
     <row r="29" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>241</v>
+        <v>28</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="F29" s="25" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G29" s="21" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H29" s="22" t="s">
         <v>3</v>
@@ -5566,31 +3625,31 @@
     </row>
     <row r="30" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C30" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F30" s="25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G30" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="H30" s="21" t="s">
         <v>31</v>
       </c>
+      <c r="H30" s="22" t="s">
+        <v>3</v>
+      </c>
       <c r="I30" s="23" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J30" s="22" t="s">
         <v>0</v>
@@ -5601,31 +3660,31 @@
     </row>
     <row r="31" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C31" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D31" s="25" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F31" s="25" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G31" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H31" s="22" t="s">
-        <v>3</v>
-      </c>
       <c r="I31" s="23" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J31" s="22" t="s">
         <v>0</v>
@@ -5636,31 +3695,31 @@
     </row>
     <row r="32" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C32" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E32" s="25" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F32" s="25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="H32" s="21" t="s">
         <v>31</v>
       </c>
+      <c r="H32" s="22" t="s">
+        <v>3</v>
+      </c>
       <c r="I32" s="23" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J32" s="22" t="s">
         <v>0</v>
@@ -5671,34 +3730,34 @@
     </row>
     <row r="33" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D33" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="26" t="s">
-        <v>6</v>
+        <v>246</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>244</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G33" s="21" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I33" s="23" t="s">
         <v>13</v>
       </c>
       <c r="J33" s="22" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K33" s="24" t="s">
         <v>6</v>
@@ -5706,28 +3765,28 @@
     </row>
     <row r="34" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C34" s="20" t="s">
         <v>126</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E34" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G34" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H34" s="21" t="s">
-        <v>252</v>
+        <v>35</v>
       </c>
       <c r="I34" s="23" t="s">
         <v>13</v>
@@ -5741,28 +3800,28 @@
     </row>
     <row r="35" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C35" s="20" t="s">
         <v>126</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E35" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G35" s="21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>43</v>
+        <v>251</v>
       </c>
       <c r="I35" s="23" t="s">
         <v>13</v>
@@ -5776,28 +3835,28 @@
     </row>
     <row r="36" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C36" s="20" t="s">
         <v>126</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E36" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H36" s="21" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I36" s="23" t="s">
         <v>13</v>
@@ -5811,34 +3870,34 @@
     </row>
     <row r="37" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E37" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="I37" s="23" t="s">
         <v>13</v>
       </c>
       <c r="J37" s="22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K37" s="24" t="s">
         <v>6</v>
@@ -5846,34 +3905,34 @@
     </row>
     <row r="38" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C38" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E38" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G38" s="21" t="s">
         <v>11</v>
       </c>
       <c r="H38" s="21" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="I38" s="23" t="s">
         <v>13</v>
       </c>
       <c r="J38" s="22" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K38" s="24" t="s">
         <v>6</v>
@@ -5881,34 +3940,34 @@
     </row>
     <row r="39" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C39" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E39" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G39" s="21" t="s">
         <v>11</v>
       </c>
       <c r="H39" s="21" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="I39" s="23" t="s">
         <v>13</v>
       </c>
       <c r="J39" s="22" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K39" s="24" t="s">
         <v>6</v>
@@ -5916,34 +3975,34 @@
     </row>
     <row r="40" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C40" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E40" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G40" s="21" t="s">
         <v>11</v>
       </c>
       <c r="H40" s="21" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="I40" s="23" t="s">
         <v>13</v>
       </c>
       <c r="J40" s="22" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K40" s="24" t="s">
         <v>6</v>
@@ -5951,34 +4010,34 @@
     </row>
     <row r="41" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C41" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E41" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G41" s="21" t="s">
         <v>11</v>
       </c>
       <c r="H41" s="21" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="I41" s="23" t="s">
         <v>13</v>
       </c>
       <c r="J41" s="22" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K41" s="24" t="s">
         <v>6</v>
@@ -5986,34 +4045,34 @@
     </row>
     <row r="42" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C42" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E42" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G42" s="21" t="s">
         <v>11</v>
       </c>
       <c r="H42" s="21" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="I42" s="23" t="s">
         <v>13</v>
       </c>
       <c r="J42" s="22" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K42" s="24" t="s">
         <v>6</v>
@@ -6021,34 +4080,34 @@
     </row>
     <row r="43" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C43" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D43" s="25" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E43" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F43" s="25" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G43" s="21" t="s">
         <v>11</v>
       </c>
       <c r="H43" s="21" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="I43" s="23" t="s">
         <v>13</v>
       </c>
       <c r="J43" s="22" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K43" s="24" t="s">
         <v>6</v>
@@ -6056,22 +4115,22 @@
     </row>
     <row r="44" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C44" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E44" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="G44" s="21" t="s">
         <v>11</v>
@@ -6091,34 +4150,34 @@
     </row>
     <row r="45" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C45" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E45" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G45" s="21" t="s">
         <v>11</v>
       </c>
       <c r="H45" s="21" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="I45" s="23" t="s">
         <v>13</v>
       </c>
       <c r="J45" s="22" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K45" s="24" t="s">
         <v>6</v>
@@ -6126,28 +4185,28 @@
     </row>
     <row r="46" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C46" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E46" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G46" s="21" t="s">
         <v>11</v>
       </c>
       <c r="H46" s="21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I46" s="23" t="s">
         <v>13</v>
@@ -6161,34 +4220,34 @@
     </row>
     <row r="47" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C47" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D47" s="25" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E47" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G47" s="21" t="s">
         <v>11</v>
       </c>
       <c r="H47" s="21" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="I47" s="23" t="s">
         <v>13</v>
       </c>
       <c r="J47" s="22" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K47" s="24" t="s">
         <v>6</v>
@@ -6196,22 +4255,22 @@
     </row>
     <row r="48" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C48" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E48" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G48" s="21" t="s">
         <v>11</v>
@@ -6231,34 +4290,34 @@
     </row>
     <row r="49" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C49" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D49" s="25" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E49" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G49" s="21" t="s">
         <v>11</v>
       </c>
       <c r="H49" s="21" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="I49" s="23" t="s">
         <v>13</v>
       </c>
       <c r="J49" s="22" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K49" s="24" t="s">
         <v>6</v>
@@ -6266,34 +4325,34 @@
     </row>
     <row r="50" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="19" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C50" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E50" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F50" s="25" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G50" s="21" t="s">
         <v>11</v>
       </c>
       <c r="H50" s="21" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="I50" s="23" t="s">
         <v>13</v>
       </c>
       <c r="J50" s="22" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K50" s="24" t="s">
         <v>6</v>
@@ -6301,22 +4360,22 @@
     </row>
     <row r="51" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C51" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E51" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F51" s="25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G51" s="21" t="s">
         <v>11</v>
@@ -6336,34 +4395,34 @@
     </row>
     <row r="52" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="E52" s="21" t="s">
-        <v>197</v>
+        <v>81</v>
+      </c>
+      <c r="E52" s="26" t="s">
+        <v>6</v>
       </c>
       <c r="F52" s="25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G52" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H52" s="22" t="s">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="H52" s="21" t="s">
+        <v>12</v>
       </c>
       <c r="I52" s="23" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J52" s="22" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K52" s="24" t="s">
         <v>6</v>
@@ -6371,31 +4430,31 @@
     </row>
     <row r="53" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D53" s="25" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E53" s="21" t="s">
-        <v>253</v>
+        <v>197</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G53" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="H53" s="21" t="s">
-        <v>89</v>
+        <v>86</v>
+      </c>
+      <c r="H53" s="22" t="s">
+        <v>3</v>
       </c>
       <c r="I53" s="23" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J53" s="22" t="s">
         <v>0</v>
@@ -6406,25 +4465,25 @@
     </row>
     <row r="54" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C54" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F54" s="25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G54" s="21" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="H54" s="21" t="s">
         <v>89</v>
@@ -6441,34 +4500,34 @@
     </row>
     <row r="55" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C55" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D55" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="E55" s="26" t="s">
-        <v>6</v>
+        <v>90</v>
+      </c>
+      <c r="E55" s="21" t="s">
+        <v>253</v>
       </c>
       <c r="F55" s="25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G55" s="21" t="s">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="H55" s="21" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I55" s="23" t="s">
         <v>13</v>
       </c>
       <c r="J55" s="22" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K55" s="24" t="s">
         <v>6</v>
@@ -6476,34 +4535,34 @@
     </row>
     <row r="56" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C56" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E56" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F56" s="25" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G56" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="H56" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="H56" s="22" t="s">
-        <v>3</v>
-      </c>
       <c r="I56" s="23" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J56" s="22" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K56" s="24" t="s">
         <v>6</v>
@@ -6511,25 +4570,25 @@
     </row>
     <row r="57" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="19" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D57" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="E57" s="21" t="s">
-        <v>198</v>
+        <v>97</v>
+      </c>
+      <c r="E57" s="26" t="s">
+        <v>6</v>
       </c>
       <c r="F57" s="25" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G57" s="21" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H57" s="22" t="s">
         <v>3</v>
@@ -6546,31 +4605,31 @@
     </row>
     <row r="58" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D58" s="25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>253</v>
+        <v>198</v>
       </c>
       <c r="F58" s="25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G58" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="H58" s="21" t="s">
-        <v>89</v>
+        <v>98</v>
+      </c>
+      <c r="H58" s="22" t="s">
+        <v>3</v>
       </c>
       <c r="I58" s="23" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J58" s="22" t="s">
         <v>0</v>
@@ -6581,25 +4640,25 @@
     </row>
     <row r="59" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="19" t="s">
-        <v>248</v>
+        <v>195</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C59" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D59" s="25" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E59" s="21" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F59" s="25" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G59" s="21" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="H59" s="21" t="s">
         <v>89</v>
@@ -6616,34 +4675,34 @@
     </row>
     <row r="60" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="19" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C60" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="E60" s="26" t="s">
-        <v>6</v>
+        <v>103</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>253</v>
       </c>
       <c r="F60" s="25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G60" s="21" t="s">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="H60" s="21" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I60" s="23" t="s">
         <v>13</v>
       </c>
       <c r="J60" s="22" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K60" s="24" t="s">
         <v>6</v>
@@ -6651,34 +4710,34 @@
     </row>
     <row r="61" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="19" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C61" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D61" s="25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E61" s="26" t="s">
         <v>6</v>
       </c>
       <c r="F61" s="25" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G61" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="H61" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="H61" s="22" t="s">
-        <v>3</v>
-      </c>
       <c r="I61" s="23" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J61" s="22" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K61" s="24" t="s">
         <v>6</v>
@@ -6686,31 +4745,31 @@
     </row>
     <row r="62" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="19" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="E62" s="21" t="s">
-        <v>199</v>
+        <v>107</v>
+      </c>
+      <c r="E62" s="26" t="s">
+        <v>6</v>
       </c>
       <c r="F62" s="25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G62" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="H62" s="21" t="s">
-        <v>112</v>
+        <v>95</v>
+      </c>
+      <c r="H62" s="22" t="s">
+        <v>3</v>
       </c>
       <c r="I62" s="23" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J62" s="22" t="s">
         <v>0</v>
@@ -6721,28 +4780,28 @@
     </row>
     <row r="63" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="19" t="s">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D63" s="25" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E63" s="21" t="s">
-        <v>255</v>
+        <v>199</v>
       </c>
       <c r="F63" s="25" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G63" s="21" t="s">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="H63" s="21" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="I63" s="23" t="s">
         <v>13</v>
@@ -6756,25 +4815,25 @@
     </row>
     <row r="64" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="19" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C64" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D64" s="25" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E64" s="21" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F64" s="25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G64" s="21" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="H64" s="21" t="s">
         <v>89</v>
@@ -6791,34 +4850,34 @@
     </row>
     <row r="65" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="19" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C65" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D65" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="E65" s="26" t="s">
-        <v>6</v>
+        <v>115</v>
+      </c>
+      <c r="E65" s="21" t="s">
+        <v>255</v>
       </c>
       <c r="F65" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G65" s="21" t="s">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="H65" s="21" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I65" s="23" t="s">
         <v>13</v>
       </c>
       <c r="J65" s="22" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K65" s="24" t="s">
         <v>6</v>
@@ -6826,71 +4885,106 @@
     </row>
     <row r="66" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="19" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C66" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D66" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E66" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F66" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="G66" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="H66" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="I66" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J66" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K66" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="C67" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D67" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="E66" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F66" s="25" t="s">
+      <c r="E67" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F67" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="G66" s="21" t="s">
+      <c r="G67" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="H66" s="22" t="s">
+      <c r="H67" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="I66" s="23" t="s">
+      <c r="I67" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="J66" s="22" t="s">
+      <c r="J67" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="K66" s="24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="11" t="s">
+      <c r="K67" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="B67" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="C67" s="20" t="s">
+      <c r="B68" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C68" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="D67" s="13" t="s">
+      <c r="D68" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="E67" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" s="13" t="s">
+      <c r="E68" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F68" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="G67" s="15" t="s">
+      <c r="G68" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="H67" s="15" t="s">
+      <c r="H68" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="I67" s="16" t="s">
+      <c r="I68" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="J67" s="17" t="s">
+      <c r="J68" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K67" s="18" t="s">
+      <c r="K68" s="18" t="s">
         <v>6</v>
       </c>
     </row>
@@ -6930,7 +5024,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>C2:C67</xm:sqref>
+          <xm:sqref>C2:C68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="42" operator="equal" id="{E9C2B272-84B1-4809-B303-CE13207E6AB0}">
@@ -6959,7 +5053,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>I2:I67</xm:sqref>
+          <xm:sqref>I2:I68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="37" operator="equal" id="{6B56C5F3-9AF3-4BD5-87CE-CADFFFDFA65E}">
@@ -7001,7 +5095,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>J2:J67</xm:sqref>
+          <xm:sqref>J2:J68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="77" id="{C74CA95C-7727-418A-BE78-990F3D7CE068}">
@@ -7043,7 +5137,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>A2:K67</xm:sqref>
+          <xm:sqref>A2:K68</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -7053,25 +5147,25 @@
           <x14:formula1>
             <xm:f>Support!$A$4:$A$5</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I67</xm:sqref>
+          <xm:sqref>I2:I68</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Support!$A$8:$A$10</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J67</xm:sqref>
+          <xm:sqref>J2:J68</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Support!$A$13:$A$14</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C67</xm:sqref>
+          <xm:sqref>C2:C68</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Support!$A$17:$A$19</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B67</xm:sqref>
+          <xm:sqref>B2:B68</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7148,17 +5242,17 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/RESTful-booker-service-api.xlsx
+++ b/RESTful-booker-service-api.xlsx
@@ -15,6 +15,10 @@
     <sheet name="REST-API-v1.0.0" sheetId="1" r:id="rId1"/>
     <sheet name="Support" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'REST-API-v1.0.0'!$A$2:$K$68</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="0">'REST-API-v1.0.0'!$A$2:$K$68</definedName>
+  </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -890,7 +894,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -916,8 +920,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -944,7 +954,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1"/>
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1095,7 +1111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -1169,453 +1185,27 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="77">
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="23">
     <dxf>
       <font>
         <color auto="1"/>
@@ -1732,42 +1322,74 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
+        <sz val="11"/>
+        <color theme="0"/>
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1791,9 +1413,7 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1825,6 +1445,26 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1881,42 +1521,26 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1973,24 +1597,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -2011,128 +1617,6 @@
           <color indexed="64"/>
         </horizontal>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2187,24 +1671,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -2218,79 +1684,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
         <vertical style="thin">
           <color indexed="64"/>
         </vertical>
@@ -2313,21 +1706,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RESTful_booker_service_api_v1_0_0" displayName="RESTful_booker_service_api_v1_0_0" ref="A1:K68" headerRowCount="0" totalsRowShown="0" headerRowDxfId="76" dataDxfId="75" tableBorderDxfId="74" totalsRowBorderDxfId="73">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RESTful_booker_service_api_v1_0_0" displayName="RESTful_booker_service_api_v1_0_0" ref="A1:K68" totalsRowShown="0" headerRowDxfId="11" dataDxfId="14" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K68"/>
   <tableColumns count="11">
-    <tableColumn id="12" name="Column12" headerRowDxfId="72" dataDxfId="71"/>
-    <tableColumn id="1" name="Column1" headerRowDxfId="70" dataDxfId="69"/>
-    <tableColumn id="3" name="Column4" headerRowDxfId="68" dataDxfId="67"/>
-    <tableColumn id="2" name="Column3" headerRowDxfId="66" dataDxfId="65"/>
-    <tableColumn id="4" name="Column5" headerRowDxfId="64" dataDxfId="63"/>
-    <tableColumn id="5" name="Column6" headerRowDxfId="62" dataDxfId="61"/>
-    <tableColumn id="13" name="Column2" headerRowDxfId="60"/>
-    <tableColumn id="14" name="Column11" headerRowDxfId="59"/>
-    <tableColumn id="6" name="Column7" headerRowDxfId="58" dataDxfId="57"/>
-    <tableColumn id="7" name="Column8" headerRowDxfId="56" dataDxfId="55"/>
-    <tableColumn id="9" name="Column10" headerRowDxfId="54" dataDxfId="53"/>
+    <tableColumn id="12" name="ID" dataDxfId="22"/>
+    <tableColumn id="1" name="TAG" dataDxfId="21"/>
+    <tableColumn id="3" name="TYPE" dataDxfId="10"/>
+    <tableColumn id="2" name="TITLE" dataDxfId="20"/>
+    <tableColumn id="4" name="PRECONDITIONS" dataDxfId="19"/>
+    <tableColumn id="5" name="STEPS" dataDxfId="18"/>
+    <tableColumn id="13" name="EXPECTED"/>
+    <tableColumn id="14" name="ACTUAL"/>
+    <tableColumn id="6" name="STATUS" dataDxfId="17"/>
+    <tableColumn id="7" name="PRIORITY" dataDxfId="16"/>
+    <tableColumn id="9" name="NOTES" dataDxfId="15"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight16" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -2598,7 +1992,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.44140625" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.44140625" customWidth="1"/>
     <col min="4" max="4" width="36.109375" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
@@ -2610,38 +2004,38 @@
     <col min="11" max="11" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:11" s="28" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="31" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2960,7 +2354,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>147</v>
       </c>
@@ -2995,7 +2389,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>148</v>
       </c>
@@ -3030,7 +2424,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>149</v>
       </c>
@@ -3065,7 +2459,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>150</v>
       </c>
@@ -3100,7 +2494,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>151</v>
       </c>
@@ -3135,7 +2529,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>152</v>
       </c>
@@ -3170,7 +2564,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>153</v>
       </c>
@@ -3205,7 +2599,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>154</v>
       </c>
@@ -3240,7 +2634,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>155</v>
       </c>
@@ -3275,7 +2669,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>156</v>
       </c>
@@ -3310,7 +2704,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
         <v>157</v>
       </c>
@@ -3341,9 +2735,9 @@
       <c r="J21" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="K21" s="30"/>
-    </row>
-    <row r="22" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K21" s="27"/>
+    </row>
+    <row r="22" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
         <v>158</v>
       </c>
@@ -3378,7 +2772,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
         <v>159</v>
       </c>
@@ -3413,7 +2807,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
         <v>160</v>
       </c>
@@ -3448,7 +2842,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
         <v>161</v>
       </c>
@@ -3483,7 +2877,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
         <v>162</v>
       </c>
@@ -3518,7 +2912,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
         <v>163</v>
       </c>
@@ -3553,7 +2947,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
         <v>164</v>
       </c>
@@ -3588,7 +2982,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
         <v>165</v>
       </c>
@@ -3623,7 +3017,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="19" t="s">
         <v>166</v>
       </c>
@@ -3658,7 +3052,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19" t="s">
         <v>167</v>
       </c>
@@ -3693,7 +3087,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
         <v>168</v>
       </c>
@@ -3728,7 +3122,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="19" t="s">
         <v>169</v>
       </c>
@@ -3763,7 +3157,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
         <v>170</v>
       </c>
@@ -3798,7 +3192,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="19" t="s">
         <v>171</v>
       </c>
@@ -3833,7 +3227,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="19" t="s">
         <v>172</v>
       </c>
@@ -3868,7 +3262,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="19" t="s">
         <v>173</v>
       </c>
@@ -3903,7 +3297,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="19" t="s">
         <v>174</v>
       </c>
@@ -3938,7 +3332,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="19" t="s">
         <v>175</v>
       </c>
@@ -3973,7 +3367,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="19" t="s">
         <v>176</v>
       </c>
@@ -4008,7 +3402,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="19" t="s">
         <v>177</v>
       </c>
@@ -4043,7 +3437,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="19" t="s">
         <v>178</v>
       </c>
@@ -4078,7 +3472,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="19" t="s">
         <v>179</v>
       </c>
@@ -4113,7 +3507,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="19" t="s">
         <v>180</v>
       </c>
@@ -4148,7 +3542,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="19" t="s">
         <v>181</v>
       </c>
@@ -4183,7 +3577,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="19" t="s">
         <v>182</v>
       </c>
@@ -4218,7 +3612,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="19" t="s">
         <v>183</v>
       </c>
@@ -4253,7 +3647,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="19" t="s">
         <v>184</v>
       </c>
@@ -4288,7 +3682,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="19" t="s">
         <v>185</v>
       </c>
@@ -4323,7 +3717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="19" t="s">
         <v>186</v>
       </c>
@@ -4358,7 +3752,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="19" t="s">
         <v>187</v>
       </c>
@@ -4393,7 +3787,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="19" t="s">
         <v>188</v>
       </c>
@@ -4428,7 +3822,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="19" t="s">
         <v>189</v>
       </c>
@@ -4463,7 +3857,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="19" t="s">
         <v>190</v>
       </c>
@@ -4498,7 +3892,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="19" t="s">
         <v>191</v>
       </c>
@@ -4533,7 +3927,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="19" t="s">
         <v>192</v>
       </c>
@@ -4568,7 +3962,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="19" t="s">
         <v>193</v>
       </c>
@@ -4603,7 +3997,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="19" t="s">
         <v>194</v>
       </c>
@@ -4638,7 +4032,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="19" t="s">
         <v>195</v>
       </c>
@@ -4673,7 +4067,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="19" t="s">
         <v>247</v>
       </c>
@@ -4708,7 +4102,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="19" t="s">
         <v>248</v>
       </c>
@@ -4743,7 +4137,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="19" t="s">
         <v>249</v>
       </c>
@@ -4778,7 +4172,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="19" t="s">
         <v>250</v>
       </c>
@@ -4813,7 +4207,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="19" t="s">
         <v>274</v>
       </c>
@@ -4848,7 +4242,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="19" t="s">
         <v>275</v>
       </c>
@@ -4883,7 +4277,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="19" t="s">
         <v>276</v>
       </c>
@@ -4918,7 +4312,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="19" t="s">
         <v>277</v>
       </c>
@@ -4953,7 +4347,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="11" t="s">
         <v>196</v>
       </c>
@@ -4989,6 +4383,7 @@
       </c>
     </row>
   </sheetData>
+  <dataConsolidate/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
